--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121693923</v>
+        <v>121693810</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väsbyskogen, Stora Väsby, Fogdö, Srm</t>
+          <t>Väsbyskogen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605335</v>
+        <v>605397</v>
       </c>
       <c r="R2" t="n">
-        <v>6592740</v>
+        <v>6592730</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -764,12 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hackspettshål i stam på döda och levande gamla grova tallar</t>
+          <t>Hackspetshål från spillkråka på flera (över 25) döda och levande tallar se bilder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,26 +780,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -816,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121693810</v>
+        <v>121693923</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -856,14 +836,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väsbyskogen, Srm</t>
+          <t>Väsbyskogen, Stora Väsby, Fogdö, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605397</v>
+        <v>605335</v>
       </c>
       <c r="R3" t="n">
-        <v>6592730</v>
+        <v>6592740</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -905,12 +885,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspetshål från spillkråka på flera (över 25) döda och levande tallar se bilder.</t>
+          <t>Hackspettshål i stam på döda och levande gamla grova tallar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,6 +901,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121759105</v>
+        <v>121753989</v>
       </c>
       <c r="B4" t="n">
         <v>8436</v>
@@ -970,7 +970,11 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -982,17 +986,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Lövhammar, Fogdö bygdegård, Srm</t>
+          <t>Likbrännerstenen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605351</v>
+        <v>605610</v>
       </c>
       <c r="R4" t="n">
-        <v>6592777</v>
+        <v>6592527</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1031,7 +1035,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,34 +1044,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1084,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121753989</v>
+        <v>121759105</v>
       </c>
       <c r="B5" t="n">
         <v>8436</v>
@@ -1117,11 +1095,7 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1133,17 +1107,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Likbrännerstenen, Srm</t>
+          <t>Norr om Lövhammar, Fogdö bygdegård, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605610</v>
+        <v>605351</v>
       </c>
       <c r="R5" t="n">
-        <v>6592527</v>
+        <v>6592777</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1172,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1182,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,8 +1165,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121693810</v>
+        <v>121693923</v>
       </c>
       <c r="B2" t="n">
         <v>57373</v>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väsbyskogen, Srm</t>
+          <t>Väsbyskogen, Stora Väsby, Fogdö, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605397</v>
+        <v>605335</v>
       </c>
       <c r="R2" t="n">
-        <v>6592730</v>
+        <v>6592740</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -764,12 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hackspetshål från spillkråka på flera (över 25) döda och levande tallar se bilder.</t>
+          <t>Hackspettshål i stam på döda och levande gamla grova tallar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +780,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,7 +816,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121693923</v>
+        <v>121693810</v>
       </c>
       <c r="B3" t="n">
         <v>57373</v>
@@ -836,14 +856,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väsbyskogen, Stora Väsby, Fogdö, Srm</t>
+          <t>Väsbyskogen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605335</v>
+        <v>605397</v>
       </c>
       <c r="R3" t="n">
-        <v>6592740</v>
+        <v>6592730</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -885,12 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspettshål i stam på döda och levande gamla grova tallar</t>
+          <t>Hackspetshål från spillkråka på flera (över 25) döda och levande tallar se bilder.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,26 +921,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121753989</v>
+        <v>121759105</v>
       </c>
       <c r="B4" t="n">
         <v>8436</v>
@@ -970,11 +970,7 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -986,17 +982,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Likbrännerstenen, Srm</t>
+          <t>Norr om Lövhammar, Fogdö bygdegård, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605610</v>
+        <v>605351</v>
       </c>
       <c r="R4" t="n">
-        <v>6592527</v>
+        <v>6592777</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1025,7 +1021,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1035,7 +1031,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,8 +1040,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1062,7 +1084,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121759105</v>
+        <v>121753989</v>
       </c>
       <c r="B5" t="n">
         <v>8436</v>
@@ -1095,7 +1117,11 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1107,17 +1133,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Lövhammar, Fogdö bygdegård, Srm</t>
+          <t>Likbrännerstenen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605351</v>
+        <v>605610</v>
       </c>
       <c r="R5" t="n">
-        <v>6592777</v>
+        <v>6592527</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,7 +1172,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1182,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,34 +1191,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,6 +1207,135 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122791937</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väsbyskogen, Fogdö bygdegård, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>605290</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6592929</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fogdö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växande på undersidan av granlåga liggandes i brant.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik de Joussineau</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik de Joussineau</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 59572-2024 artfynd.xlsx
+++ b/artfynd/A 59572-2024 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122791937</v>
       </c>
       <c r="B6" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
